--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484573_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484573_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2078</v>
+        <v>2.2237</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.3465</v>
+        <v>-1.9095</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5543</v>
+        <v>4.1332</v>
       </c>
       <c r="G2" t="n">
         <v>0.4462</v>
@@ -610,13 +610,13 @@
         <v>3.4819</v>
       </c>
       <c r="S2" t="n">
-        <v>1.131</v>
+        <v>0.1469</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8017</v>
+        <v>0.2387</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3293</v>
+        <v>-0.0919</v>
       </c>
       <c r="V2" t="n">
         <v>4.7459</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. CONDE BARBERA</t>
+          <t>J. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.292</v>
+        <v>1.9509</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5707</v>
+        <v>0.8143</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7213000000000001</v>
+        <v>1.1366</v>
       </c>
       <c r="G3" t="n">
-        <v>0.246</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1499</v>
+        <v>0.7402</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0961</v>
+        <v>0.2472</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0217</v>
+        <v>1.2792</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0217</v>
+        <v>0.5511</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.7282</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2243</v>
+        <v>-0.2919</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1282</v>
+        <v>0.1891</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0961</v>
+        <v>-0.481</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3665</v>
+        <v>1.6493</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3665</v>
+        <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6796</v>
+        <v>-0.0418</v>
       </c>
       <c r="T3" t="n">
-        <v>0.549</v>
+        <v>-0.2816</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1305</v>
+        <v>0.2398</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MARIA VENTURA</t>
+          <t>J. CONDE BARBERA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6723</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0311</v>
+        <v>0.1861</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6412</v>
+        <v>0.6966</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.246</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7402</v>
+        <v>0.1499</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2472</v>
+        <v>0.0961</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2792</v>
+        <v>0.0217</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5511</v>
+        <v>0.0217</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7282</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2919</v>
+        <v>0.2243</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1891</v>
+        <v>0.1282</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.481</v>
+        <v>0.0961</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6493</v>
+        <v>0.3665</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8326</v>
+        <v>0.3665</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3205</v>
+        <v>0.2702</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0648</v>
+        <v>0.1644</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2557</v>
+        <v>0.1058</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. CALANCHE GONZÁLEZ</t>
+          <t>J. CARRERAS GARRIGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6251</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6251</v>
+        <v>0.0566</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.6828</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6251</v>
+        <v>0.7897</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.8218</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6251</v>
+        <v>-0.0321</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6251</v>
+        <v>0.6936</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.6936</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6251</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.0961</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.1282</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.0321</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-0.0139</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.0369</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. CARRERAS GARRIGA</t>
+          <t>L. MONTANES RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5441</v>
+        <v>0.7119</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0396</v>
+        <v>-1.0571</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5837</v>
+        <v>1.769</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7897</v>
+        <v>-1.0106</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8218</v>
+        <v>0.5183</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0321</v>
+        <v>-1.5289</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6936</v>
+        <v>-0.841</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6936</v>
+        <v>0.3993</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-1.2404</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0961</v>
+        <v>-0.1695</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1282</v>
+        <v>0.119</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0321</v>
+        <v>-0.2885</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1722</v>
+        <v>-0.1284</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1101</v>
+        <v>-0.2161</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0621</v>
+        <v>0.0877</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6231</v>
+        <v>0.9346</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.9346</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. MONTANES RUIZ</t>
+          <t>M. CALANCHE GONZÁLEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4424</v>
+        <v>0.6251</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1533</v>
+        <v>0.6251</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5956</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0106</v>
+        <v>0.6251</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5183</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5289</v>
+        <v>0.6251</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.841</v>
+        <v>0.6251</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3993</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2404</v>
+        <v>0.6251</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1695</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.119</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2885</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.398</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3122</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0858</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9346</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9346</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2924</v>
+        <v>0.0694</v>
       </c>
       <c r="E8" t="n">
         <v>0.5641</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2717</v>
+        <v>-0.4946</v>
       </c>
       <c r="G8" t="n">
         <v>0.2962</v>
@@ -1078,13 +1078,13 @@
         <v>0.5498</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7133</v>
+        <v>0.4904</v>
       </c>
       <c r="T8" t="n">
         <v>0.1456</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5678</v>
+        <v>0.3448</v>
       </c>
       <c r="V8" t="n">
         <v>-1.267</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0985</v>
+        <v>-0.5854</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2514</v>
+        <v>-2.9105</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3499</v>
+        <v>2.3251</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2613</v>
@@ -1156,13 +1156,13 @@
         <v>2.1991</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3756</v>
+        <v>0.6917</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4442</v>
+        <v>0.7851</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.06859999999999999</v>
+        <v>-0.0934</v>
       </c>
       <c r="V9" t="n">
         <v>0.6335</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0571</v>
+        <v>-1.7875</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5473</v>
+        <v>-0.4511</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5098</v>
+        <v>-1.3364</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7587</v>
@@ -1234,13 +1234,13 @@
         <v>0.5498</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8927</v>
+        <v>-0.6231</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3673</v>
+        <v>-0.2711</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5254</v>
+        <v>-0.352</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9554</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2242</v>
+        <v>-1.9348</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8981</v>
+        <v>-1.9803</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3261</v>
+        <v>0.0455</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4785</v>
@@ -1312,13 +1312,13 @@
         <v>2.5656</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4762</v>
+        <v>-1.1868</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1131</v>
+        <v>-0.1953</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3631</v>
+        <v>-0.9915</v>
       </c>
       <c r="V11" t="n">
         <v>-2.8351</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9553</v>
+        <v>-3.0799</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3001</v>
+        <v>-2.8054</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3448</v>
+        <v>-0.2745</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6909</v>
@@ -1390,13 +1390,13 @@
         <v>3.2986</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4476</v>
+        <v>-0.5722</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0294</v>
+        <v>-0.5347</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5818</v>
+        <v>-0.0376</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5984</v>
+        <v>-5.9254</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.7336</v>
+        <v>-6.0605</v>
       </c>
       <c r="F13" t="n">
         <v>0.1351</v>
@@ -1468,10 +1468,10 @@
         <v>2.0158</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8507</v>
+        <v>-1.1776</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2481</v>
+        <v>-0.575</v>
       </c>
       <c r="U13" t="n">
         <v>-0.6026</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.6604</v>
+        <v>-6.109999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-15.4789</v>
+        <v>-14.9282</v>
       </c>
       <c r="F14" t="n">
-        <v>8.818299999999999</v>
+        <v>8.8184</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.6409</v>
+        <v>-3.640900000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>6.456400000000001</v>
+        <v>6.456400000000002</v>
       </c>
       <c r="I14" t="n">
         <v>-10.0973</v>
@@ -1546,13 +1546,13 @@
         <v>18.3258</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.6584</v>
+        <v>-2.1077</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3045</v>
+        <v>-0.7538999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.3539</v>
+        <v>-1.354</v>
       </c>
       <c r="V14" t="n">
         <v>-1.277500000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N. CARPITELLI</t>
+          <t>L. ALBEROLA GUILLOT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8185</v>
+        <v>5.6067</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7924</v>
+        <v>2.1877</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0261</v>
+        <v>3.419</v>
       </c>
       <c r="G15" t="n">
-        <v>1.884</v>
+        <v>3.4831</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5059</v>
+        <v>0.8255</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3781</v>
+        <v>2.6576</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4555</v>
+        <v>3.754</v>
       </c>
       <c r="K15" t="n">
-        <v>0.622</v>
+        <v>0.9997</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8335</v>
+        <v>2.7543</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4285</v>
+        <v>-0.2709</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1161</v>
+        <v>-0.1742</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5446</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8326</v>
+        <v>-4.5814</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8326</v>
+        <v>2.7489</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4952</v>
+        <v>0.7057</v>
       </c>
       <c r="T15" t="n">
-        <v>2.4706</v>
+        <v>-0.173</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0246</v>
+        <v>0.8787</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5608</v>
+        <v>3.2506</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.3011</v>
+        <v>3.1882</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2596</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. ALBEROLA GUILLOT</t>
+          <t>N. CARPITELLI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.7055</v>
+        <v>2.8675</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7454</v>
+        <v>0.2539</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9601</v>
+        <v>2.6136</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4831</v>
+        <v>1.884</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8255</v>
+        <v>0.5059</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6576</v>
+        <v>1.3781</v>
       </c>
       <c r="J16" t="n">
-        <v>3.754</v>
+        <v>1.4555</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9997</v>
+        <v>0.622</v>
       </c>
       <c r="L16" t="n">
-        <v>2.7543</v>
+        <v>0.8335</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2709</v>
+        <v>0.4285</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1742</v>
+        <v>-0.1161</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.09669999999999999</v>
+        <v>0.5446</v>
       </c>
       <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-1.8326</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-4.5814</v>
-      </c>
       <c r="R16" t="n">
-        <v>2.7489</v>
+        <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1956</v>
+        <v>1.5443</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.6153</v>
+        <v>0.9322</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4198</v>
+        <v>0.6121</v>
       </c>
       <c r="V16" t="n">
-        <v>3.2506</v>
+        <v>-0.5608</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1882</v>
+        <v>-0.3011</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0623</v>
+        <v>-0.2596</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>J. CLIMENT GOMIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0089</v>
+        <v>2.8211</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0392</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9697</v>
+        <v>2.0525</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2149</v>
+        <v>0.1951</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5672</v>
+        <v>-0.5455</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7821</v>
+        <v>0.7406</v>
       </c>
       <c r="J17" t="n">
-        <v>0.73</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.155</v>
+        <v>-0.7743</v>
       </c>
       <c r="L17" t="n">
-        <v>0.885</v>
+        <v>0.8691</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4849</v>
+        <v>0.1003</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4122</v>
+        <v>0.2288</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8971</v>
+        <v>-0.1285</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0158</v>
+        <v>1.8326</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3287</v>
+        <v>0.3805</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3092</v>
+        <v>0.3232</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.638</v>
+        <v>0.0573</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8931</v>
+        <v>1.3293</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8931</v>
+        <v>0.0623</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CLIMENT GOMIS</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.437</v>
+        <v>2.5117</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2891</v>
+        <v>0.9431</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7261</v>
+        <v>1.5686</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1951</v>
+        <v>1.2149</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5455</v>
+        <v>-0.5672</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7406</v>
+        <v>1.7821</v>
       </c>
       <c r="J18" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7743</v>
+        <v>-0.155</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8691</v>
+        <v>0.885</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1003</v>
+        <v>0.4849</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2288</v>
+        <v>-0.4122</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1285</v>
+        <v>0.8971</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9163</v>
+        <v>2.0158</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8326</v>
+        <v>2.0158</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0036</v>
+        <v>0.174</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7345</v>
+        <v>0.2131</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2691</v>
+        <v>-0.0391</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3293</v>
+        <v>-0.8931</v>
       </c>
       <c r="W18" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0623</v>
+        <v>-0.8931</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7242</v>
+        <v>0.8583</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4893</v>
+        <v>0.297</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2349</v>
+        <v>0.5613</v>
       </c>
       <c r="G20" t="n">
         <v>3.1977</v>
@@ -2014,13 +2014,13 @@
         <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4428</v>
+        <v>0.5769</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4389</v>
+        <v>0.2466</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0039</v>
+        <v>0.3303</v>
       </c>
       <c r="V20" t="n">
         <v>-1.267</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4651</v>
+        <v>0.6924</v>
       </c>
       <c r="E21" t="n">
         <v>0.1149</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3502</v>
+        <v>0.5775</v>
       </c>
       <c r="G21" t="n">
         <v>0.3809</v>
@@ -2092,13 +2092,13 @@
         <v>0.5498</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4656</v>
+        <v>-0.2383</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2753</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1903</v>
+        <v>0.0369</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ESTARLICH MARTINEZ</t>
+          <t>M. GONZALEZ MAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2467</v>
+        <v>0.1254</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6092</v>
+        <v>-0.5959</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3625</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0653</v>
+        <v>1.4037</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3313</v>
+        <v>-0.3145</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7339</v>
+        <v>1.7182</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4907</v>
+        <v>1.3336</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.0778</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.413</v>
+        <v>1.3336</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5745</v>
+        <v>0.0701</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2535</v>
+        <v>-0.3145</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.321</v>
+        <v>0.3846</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3665</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3823</v>
+        <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5443</v>
+        <v>0.0045</v>
       </c>
       <c r="T22" t="n">
-        <v>0.675</v>
+        <v>-0.0969</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1307</v>
+        <v>0.1014</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6408</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. GONZALEZ MAS</t>
+          <t>J. ESTARLICH MARTINEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3408</v>
+        <v>-0.3326</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8844</v>
+        <v>-2.8976</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5436</v>
+        <v>2.565</v>
       </c>
       <c r="G23" t="n">
-        <v>1.4037</v>
+        <v>-2.0653</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3145</v>
+        <v>-1.3313</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7182</v>
+        <v>-0.7339</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3336</v>
+        <v>-1.4907</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-1.0778</v>
       </c>
       <c r="L23" t="n">
-        <v>1.3336</v>
+        <v>-0.413</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0701</v>
+        <v>-0.5745</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3145</v>
+        <v>-0.2535</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3846</v>
+        <v>-0.321</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.2828</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5498</v>
+        <v>2.3823</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4617</v>
+        <v>0.4583</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3854</v>
+        <v>0.3865</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.07630000000000001</v>
+        <v>0.0718</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.6408</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.6854</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4596</v>
+        <v>-0.6664</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.2366</v>
+        <v>-1.6212</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7771</v>
+        <v>0.9548</v>
       </c>
       <c r="G24" t="n">
         <v>-0.4006</v>
@@ -2326,13 +2326,13 @@
         <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3075</v>
+        <v>0.1007</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2557</v>
+        <v>-0.129</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0519</v>
+        <v>0.2296</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.6117</v>
+        <v>-1.6729</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4703</v>
+        <v>-1.7588</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1414</v>
+        <v>0.0859</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6379</v>
@@ -2404,13 +2404,13 @@
         <v>1.0995</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2486</v>
+        <v>0.1874</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2911</v>
+        <v>0.0027</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0426</v>
+        <v>0.1847</v>
       </c>
       <c r="V25" t="n">
         <v>-0.3219</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.0356</v>
+        <v>-2.0794</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.8983</v>
+        <v>-3.8021</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8627</v>
+        <v>1.7227</v>
       </c>
       <c r="G26" t="n">
         <v>-1.9662</v>
@@ -2482,13 +2482,13 @@
         <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4333</v>
+        <v>0.3895</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1116</v>
+        <v>-0.0154</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.405</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2357</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.7546</v>
+        <v>-3.0985</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.562</v>
+        <v>-3.6581</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8074</v>
+        <v>0.5596</v>
       </c>
       <c r="G27" t="n">
         <v>-1.9986</v>
@@ -2560,13 +2560,13 @@
         <v>1.0995</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6418</v>
+        <v>0.2979</v>
       </c>
       <c r="T27" t="n">
-        <v>0.0355</v>
+        <v>-0.0607</v>
       </c>
       <c r="U27" t="n">
-        <v>0.6063</v>
+        <v>0.3586</v>
       </c>
       <c r="V27" t="n">
         <v>-0.6647</v>
@@ -2593,16 +2593,16 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>6.660400000000001</v>
+        <v>8.583500000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-8.8185</v>
+        <v>-8.818300000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>15.479</v>
+        <v>17.4018</v>
       </c>
       <c r="G28" t="n">
-        <v>3.641000000000001</v>
+        <v>3.640999999999999</v>
       </c>
       <c r="H28" t="n">
         <v>-6.456300000000001</v>
@@ -2620,7 +2620,7 @@
         <v>9.298699999999998</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3168</v>
+        <v>-0.3168000000000002</v>
       </c>
       <c r="N28" t="n">
         <v>-1.1153</v>
@@ -2638,13 +2638,13 @@
         <v>17.4094</v>
       </c>
       <c r="S28" t="n">
-        <v>2.6583</v>
+        <v>4.581399999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>1.3539</v>
+        <v>1.354</v>
       </c>
       <c r="U28" t="n">
-        <v>1.3044</v>
+        <v>3.227300000000001</v>
       </c>
       <c r="V28" t="n">
         <v>1.2775</v>
